--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:31</t>
+          <t>2026-10-14 14:14:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-ColumnShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-ColumnShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:50</t>
+          <t>2026-10-14 14:30:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:ColumnShape</t>
+          <t>hrishapes:ColumnShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#ColumnShape</t>
+          <t>http://data.health-ri.nl/core/p2/ColumnShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:ColumnShape/csvw:name</t>
+          <t>hrishapes:ColumnShape#csvw:name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:ColumnShape</t>
+          <t>hrishapes:ColumnShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1746,12 +1763,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:ColumnShape/csvw:title</t>
+          <t>hrishapes:ColumnShape#csvw:title</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:ColumnShape</t>
+          <t>hrishapes:ColumnShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1808,12 +1825,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hri:ColumnShape/dct:description</t>
+          <t>hrishapes:ColumnShape#dct:description</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hri:ColumnShape</t>
+          <t>hrishapes:ColumnShape</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1870,12 +1887,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hri:ColumnShape/csvw:datatype</t>
+          <t>hrishapes:ColumnShape#csvw:datatype</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hri:ColumnShape</t>
+          <t>hrishapes:ColumnShape</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1932,12 +1949,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hri:ColumnShape/csvw:propertyUrl</t>
+          <t>hrishapes:ColumnShape#csvw:propertyUrl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hri:ColumnShape</t>
+          <t>hrishapes:ColumnShape</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:39</t>
+          <t>2026-10-19 15:50:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dash:TextAreaEditor</t>
+          <t>dash:TextFieldEditor</t>
         </is>
       </c>
     </row>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:04</t>
+          <t>2026-10-26 13:15:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:51</t>
+          <t>2026-10-26 16:19:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:40</t>
+          <t>2026-10-27 15:44:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:14</t>
+          <t>2026-10-28 09:50:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-column.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:43</t>
+          <t>2026-10-28 11:04:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
